--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B306915E-B96E-48E6-A3AE-5AA0BCD18F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62472812-89EA-4D64-930E-B6E3108424CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -207,6 +207,15 @@
   <si>
     <t>Felt a bit tired after class and slept in the evening.</t>
   </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>independeance day</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
 </sst>
 </file>
 
@@ -370,12 +379,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -390,6 +393,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -876,74 +885,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="21">
         <v>12617353</v>
       </c>
-      <c r="G2" s="16"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="20"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -990,48 +999,48 @@
       </c>
     </row>
     <row r="6" spans="1:14" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="A6" s="13">
         <v>46247</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="14">
         <v>340</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="14">
         <v>30</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="14">
         <v>60</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="14">
         <v>30</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="14">
         <v>400</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="14">
         <v>8</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="14">
         <v>40</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="15">
         <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>900</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="15">
         <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
         <v>540</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="M6" s="20" t="s">
+      <c r="M6" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="N6" s="17" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1080,47 +1089,93 @@
       <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10" t="str">
+      <c r="A8" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="9">
+        <v>540</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>120</v>
+      </c>
+      <c r="E8" s="9">
+        <v>60</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>50</v>
+      </c>
+      <c r="I8" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="10" t="str">
+        <v>770</v>
+      </c>
+      <c r="J8" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="12"/>
+        <v>670</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10" t="str">
+      <c r="A9" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B9" s="9">
+        <v>500</v>
+      </c>
+      <c r="C9" s="9">
+        <v>60</v>
+      </c>
+      <c r="D9" s="9">
+        <v>120</v>
+      </c>
+      <c r="E9" s="9">
+        <v>50</v>
+      </c>
+      <c r="F9" s="9">
+        <v>0</v>
+      </c>
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
+        <v>60</v>
+      </c>
+      <c r="I9" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="10" t="str">
+        <v>790</v>
+      </c>
+      <c r="J9" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
+        <v>650</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62472812-89EA-4D64-930E-B6E3108424CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A411D5D7-F34D-41EC-A85E-F44AFAD14781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>High</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>Low</t>
   </si>
 </sst>
 </file>
@@ -878,7 +884,7 @@
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="28" customWidth="1"/>
@@ -1179,47 +1185,91 @@
       <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10" t="str">
+      <c r="A10" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="9">
+        <v>410</v>
+      </c>
+      <c r="C10" s="9">
+        <v>20</v>
+      </c>
+      <c r="D10" s="9">
+        <v>35</v>
+      </c>
+      <c r="E10" s="9">
+        <v>35</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>120</v>
+      </c>
+      <c r="I10" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="10" t="str">
+        <v>620</v>
+      </c>
+      <c r="J10" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
+        <v>820</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N10" s="12"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10" t="str">
+      <c r="A11" s="8">
+        <v>46252</v>
+      </c>
+      <c r="B11" s="9">
+        <v>430</v>
+      </c>
+      <c r="C11" s="9">
+        <v>90</v>
+      </c>
+      <c r="D11" s="9">
+        <v>60</v>
+      </c>
+      <c r="E11" s="9">
+        <v>50</v>
+      </c>
+      <c r="F11" s="9">
+        <v>400</v>
+      </c>
+      <c r="G11" s="9">
+        <v>8</v>
+      </c>
+      <c r="H11" s="9">
+        <v>60</v>
+      </c>
+      <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="10" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
+        <v>350</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>61</v>
+      </c>
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A411D5D7-F34D-41EC-A85E-F44AFAD14781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9F553A-F9F6-4B96-82C5-91CF17176EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -221,6 +221,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1239,7 @@
         <v>430</v>
       </c>
       <c r="C11" s="9">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D11" s="9">
         <v>60</v>
@@ -1255,11 +1258,11 @@
       </c>
       <c r="I11" s="10">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1060</v>
       </c>
       <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>52</v>
@@ -1273,25 +1276,47 @@
       <c r="N11" s="12"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+      <c r="A12" s="8">
+        <v>46253</v>
+      </c>
+      <c r="B12" s="9">
+        <v>410</v>
+      </c>
+      <c r="C12" s="9">
+        <v>60</v>
+      </c>
+      <c r="D12" s="9">
+        <v>60</v>
+      </c>
+      <c r="E12" s="9">
+        <v>40</v>
+      </c>
+      <c r="F12" s="9">
+        <v>200</v>
+      </c>
+      <c r="G12" s="9">
+        <v>4</v>
+      </c>
+      <c r="H12" s="9">
+        <v>60</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>830</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
+        <v>610</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9F553A-F9F6-4B96-82C5-91CF17176EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3486B5-F1E6-4A92-B543-EDA0C085A1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1320,25 +1320,47 @@
       <c r="N12" s="12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="A13" s="8">
+        <v>46254</v>
+      </c>
+      <c r="B13" s="9">
+        <v>410</v>
+      </c>
+      <c r="C13" s="9">
+        <v>60</v>
+      </c>
+      <c r="D13" s="9">
+        <v>30</v>
+      </c>
+      <c r="E13" s="9">
+        <v>30</v>
+      </c>
+      <c r="F13" s="9">
+        <v>300</v>
+      </c>
+      <c r="G13" s="9">
+        <v>6</v>
+      </c>
+      <c r="H13" s="9">
+        <v>120</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>950</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
+        <v>490</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3486B5-F1E6-4A92-B543-EDA0C085A1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8B3474-AE98-43D1-B832-16022EF72233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1364,25 +1364,47 @@
       <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="A14" s="8">
+        <v>46255</v>
+      </c>
+      <c r="B14" s="9">
+        <v>470</v>
+      </c>
+      <c r="C14" s="9">
+        <v>60</v>
+      </c>
+      <c r="D14" s="9">
+        <v>60</v>
+      </c>
+      <c r="E14" s="9">
+        <v>20</v>
+      </c>
+      <c r="F14" s="9">
+        <v>300</v>
+      </c>
+      <c r="G14" s="9">
+        <v>6</v>
+      </c>
+      <c r="H14" s="9">
+        <v>120</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
+        <v>410</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">

--- a/12617353.xlsx
+++ b/12617353.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saini\Downloads\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8B3474-AE98-43D1-B832-16022EF72233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABED403B-FFA2-44B3-B11C-FCC9AA8980A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1425" yWindow="1425" windowWidth="21600" windowHeight="11835" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="63">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1408,25 +1408,47 @@
       <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="A15" s="8">
+        <v>46256</v>
+      </c>
+      <c r="B15" s="9">
+        <v>640</v>
+      </c>
+      <c r="C15" s="9">
+        <v>65</v>
+      </c>
+      <c r="D15" s="9">
+        <v>0</v>
+      </c>
+      <c r="E15" s="9">
+        <v>30</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>450</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
+        <v>255</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>50</v>
+      </c>
       <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
